--- a/auditoria_sharepoint_seleniumv4.xlsx
+++ b/auditoria_sharepoint_seleniumv4.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>14s</t>
+          <t>15s</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>17s</t>
+          <t>14s</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>16s</t>
+          <t>14s</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>15s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>14s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>14s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>14s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>AULA_U1A01_Prescrição de Exercício para Grupos Especiais _ Aprovado.docx; AULA_U1A01_Prescrição de Exercício para Grupos Especiais.docx; AULA_U1A01_Prescrição de Exercício para Grupos Especiais_AJ01.docx; AULA_U1A01_Prescrição de Exercício para Grupos Especiais_REV01.docx; AULA_U1A01_Prescricao_de_Exercicio_para_Grupos_Especiais_Relatorio.pdf; BQ_U1A01_Prescrição de Exercício para Grupos Especiais _ Aprovado.docx; BQ_U1A01_Prescrição de Exercício para Grupos Especiais.docx; SL_U1A01_Prescrição de Exercício para Grupos Especiais.pptx; SL_U1A01_Prescrição de Exercício para Grupos Especiais_AJ01.pptx; SL_U1A01_Prescrição de Exercício para Grupos Especiais_REV01.pptx; .docx; .pdf; .pptx</t>
+          <t>AULA_U1A01_Prescrição de Exercício para Grupos Especiais _ Aprovado.docx; AULA_U1A01_Prescrição de Exercício para Grupos Especiais.docx; AULA_U1A01_Prescrição de Exercício para Grupos Especiais_AJ01.docx; AULA_U1A01_Prescrição de Exercício para Grupos Especiais_REV01.docx; AULA_U1A01_Prescricao_de_Exercicio_para_Grupos_Especiais_Relatorio.pdf; BQ_U1A01_Prescrição de Exercício para Grupos Especiais _ Aprovado.docx; BQ_U1A01_Prescrição de Exercício para Grupos Especiais.docx; SL_U1A01_Prescrição de Exercício para Grupos Especiais.pptx; SL_U1A01_Prescrição de Exercício para Grupos Especiais_ Aprovado.pptx; SL_U1A01_Prescrição de Exercício para Grupos Especiais_AJ01.pptx; SL_U1A01_Prescrição de Exercício para Grupos Especiais_REV01.pptx; .docx; .pdf; .pptx</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>22s</t>
+          <t>20s</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1508,18 +1508,18 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Entrega inicial completa</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>AULA_U1A02_Prescrição de Exercício para Grupos Especiais.docx; AULA_U1A02_Prescricao_de_Exercicio_para_Grupos_Especiais_Relatorio.pdf; BQ_U1A02_Prescrição de Exercício para Grupos Especiais.docx; SL_U1A02_Prescrição de Exercício para Grupos Especiais.pptx; .docx; .pdf; .pptx</t>
+          <t>AULA_U1A02_Prescrição de Exercício para Grupos Especiais _ Aprovado.docx; AULA_U1A02_Prescrição de Exercício para Grupos Especiais.docx; AULA_U1A02_Prescricao_de_Exercicio_para_Grupos_Especiais_Relatorio.pdf; BQ_U1A02_Prescrição de Exercício para Grupos Especiais _Aprovado.docx; BQ_U1A02_Prescrição de Exercício para Grupos Especiais.docx; SL_U1A02_Prescrição de Exercício para Grupos Especiais.pptx; SL_U1A02_Prescrição de Exercício para Grupos Especiais_Aprovado.pptx; .docx; .pdf; .pptx</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>17s</t>
+          <t>16s</t>
         </is>
       </c>
     </row>
@@ -1566,17 +1566,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1606,18 +1606,18 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Incompleto</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>DOCX, PPT, PDF</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
+          <t>Entrega inicial completa</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>AULA_U1A03_Prescrição de Exercício para Grupos Especiais.docx; AULA_U1A03_Prescricao_de_Exercicio_para_Grupos_Especiais_Relatorio.pdf; BQ_U1A03_Prescrição de Exercício para Grupos Especiais.docx; SL_U1A03_Prescrição de Exercício para Grupos Especiais.pptx; .docx; .pdf; .pptx</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>15s</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>11s</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>AULA_U1A01_Prescrição de Exercício para Grupos Especiais _ Aprovado.docx; AULA_U1A01_Prescrição de Exercício para Grupos Especiais.docx; AULA_U1A01_Prescrição de Exercício para Grupos Especiais_AJ01.docx; AULA_U1A01_Prescrição de Exercício para Grupos Especiais_REV01.docx; AULA_U1A01_Prescricao_de_Exercicio_para_Grupos_Especiais_Relatorio.pdf; BQ_U1A01_Prescrição de Exercício para Grupos Especiais _ Aprovado.docx; BQ_U1A01_Prescrição de Exercício para Grupos Especiais.docx; SL_U1A01_Prescrição de Exercício para Grupos Especiais.pptx; SL_U1A01_Prescrição de Exercício para Grupos Especiais_AJ01.pptx; SL_U1A01_Prescrição de Exercício para Grupos Especiais_REV01.pptx; .docx; .pdf; .pptx</t>
+          <t>AULA_U1A01_Prescrição de Exercício para Grupos Especiais _ Aprovado.docx; AULA_U1A01_Prescrição de Exercício para Grupos Especiais.docx; AULA_U1A01_Prescrição de Exercício para Grupos Especiais_AJ01.docx; AULA_U1A01_Prescrição de Exercício para Grupos Especiais_REV01.docx; AULA_U1A01_Prescricao_de_Exercicio_para_Grupos_Especiais_Relatorio.pdf; BQ_U1A01_Prescrição de Exercício para Grupos Especiais _ Aprovado.docx; BQ_U1A01_Prescrição de Exercício para Grupos Especiais.docx; SL_U1A01_Prescrição de Exercício para Grupos Especiais.pptx; SL_U1A01_Prescrição de Exercício para Grupos Especiais_ Aprovado.pptx; SL_U1A01_Prescrição de Exercício para Grupos Especiais_AJ01.pptx; SL_U1A01_Prescrição de Exercício para Grupos Especiais_REV01.pptx; .docx; .pdf; .pptx</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>22s</t>
+          <t>19s</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1998,18 +1998,18 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Entrega inicial completa</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>AULA_U1A02_Prescrição de Exercício para Grupos Especiais.docx; AULA_U1A02_Prescricao_de_Exercicio_para_Grupos_Especiais_Relatorio.pdf; BQ_U1A02_Prescrição de Exercício para Grupos Especiais.docx; SL_U1A02_Prescrição de Exercício para Grupos Especiais.pptx; .docx; .pdf; .pptx</t>
+          <t>AULA_U1A02_Prescrição de Exercício para Grupos Especiais _ Aprovado.docx; AULA_U1A02_Prescrição de Exercício para Grupos Especiais.docx; AULA_U1A02_Prescricao_de_Exercicio_para_Grupos_Especiais_Relatorio.pdf; BQ_U1A02_Prescrição de Exercício para Grupos Especiais _Aprovado.docx; BQ_U1A02_Prescrição de Exercício para Grupos Especiais.docx; SL_U1A02_Prescrição de Exercício para Grupos Especiais.pptx; SL_U1A02_Prescrição de Exercício para Grupos Especiais_Aprovado.pptx; .docx; .pdf; .pptx</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>17s</t>
+          <t>16s</t>
         </is>
       </c>
     </row>
@@ -2056,17 +2056,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2096,18 +2096,18 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Incompleto</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>DOCX, PPT, PDF</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
+          <t>Entrega inicial completa</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>AULA_U1A03_Prescrição de Exercício para Grupos Especiais.docx; AULA_U1A03_Prescricao_de_Exercicio_para_Grupos_Especiais_Relatorio.pdf; BQ_U1A03_Prescrição de Exercício para Grupos Especiais.docx; SL_U1A03_Prescrição de Exercício para Grupos Especiais.pptx; .docx; .pdf; .pptx</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>14s</t>
+          <t>15s</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>11s</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2395,13 +2395,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>DOCX, PPT, PDF</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>U1A01_Governança_E_Qualidade_De_Dados_Entrega.docx; U1A01_Governança_E_Qualidade_De_Dados_Entrega.pptx; .docx; .pptx</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>14s</t>
+          <t>13s</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2452,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2493,10 +2497,14 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>DOCX, PPT, PDF</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>U1A02_Governança_E_Qualidade_De_Dados_Entrega.docx; U1A02_Governança_E_Qualidade_De_Dados_Entrega.pptx; .docx; .pptx</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>13s</t>
@@ -2546,12 +2554,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2591,10 +2599,14 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>DOCX, PPT, PDF</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>U1A03_Governança_E_Qualidade_De_Dados_Entrega.docx; U1A03_Governança_E_Qualidade_De_Dados_Entrega.pptx; .docx; .pptx</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>13s</t>
@@ -2644,12 +2656,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2689,10 +2701,14 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>DOCX, PPT, PDF</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>U1A04_Governança_E_Qualidade_De_Dados_Entrega.docx; U1A04_Governança_E_Qualidade_De_Dados_Entrega.pptx; .docx; .pptx</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>13s</t>
@@ -2840,17 +2856,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2880,18 +2896,18 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Incompleto</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>DOCX, PPT, PDF</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
+          <t>Entrega inicial completa</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>U01A01_FUNDAMENTOSEAVALIAÇÃOEMFISIOTERAPIA_ENTREGA.docx; U01A01_FUNDAMENTOSEAVALIAÇÃOEMFISIOTERAPIA_ENTREGA.pptx; U01A01_FUNDAMENTOSEAVALIACAOEMFISIOTERAPIA_ENTREGA-report.pdf; .docx; .pptx; .pdf</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>14s</t>
+          <t>15s</t>
         </is>
       </c>
     </row>
@@ -2989,7 +3005,7 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3201,7 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
-          <t>11s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3299,7 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
-          <t>11s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3397,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>16s</t>
+          <t>18s</t>
         </is>
       </c>
     </row>
@@ -3428,22 +3444,22 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3468,18 +3484,18 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Incompleto</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>DOCX, PPT, PDF</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
+          <t>Entrega inicial completa</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>AULA2_U1A02_Fisioterapia_na_saúde_do_trabalhador.docx; AULA2_U1A02_Fisioterapia_na_saude_do_trabalhador-report.pdf; QUEST_U1A02_Fisioterapia_na_saúde_do_trabalhador.docx; SL_U1A02_Fisioterapia_na_saúde_do_trabalhador.pptx; .docx; .pdf; .pptx</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>11s</t>
+          <t>14s</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3593,7 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>11s</t>
+          <t>15s</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3856,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3860,18 +3876,18 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Entrega inicial completa</t>
+          <t>Aguardando AJ1</t>
         </is>
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>U01A01_FUNDAMENTOS DO ENVELHECIMENTO E ATENÇÃO À SAÚDE DA PESSOA IDOSA__Template_ENTREGA.docx; U01A01_FUNDAMENTOS DO ENVELHECIMENTO E ATENÇÃO À SAÚDE DA PESSOA IDOSA__Template_ENTREGA.pptx; U01A01_FUNDAMENTOSDOENVELHECIMENTOEATENCAOASAUDEDAPESSOAIDOSA_Template_ENTREGA-report.pdf; .docx; .pptx; .pdf</t>
+          <t>U01A01_Fisioterapia na Saúde do Idoso_Rev1.docx; U01A01_Fisioterapia na Saúde do Idoso_Rev1.pptx; U01A01_FUNDAMENTOS DO ENVELHECIMENTO E ATENÇÃO À SAÚDE DA PESSOA IDOSA__Template_ENTREGA.docx; U01A01_FUNDAMENTOS DO ENVELHECIMENTO E ATENÇÃO À SAÚDE DA PESSOA IDOSA__Template_ENTREGA.pptx; U01A01_FUNDAMENTOSDOENVELHECIMENTOEATENCAOASAUDEDAPESSOAIDOSA_Template_ENTREGA-report.pdf; .docx; .pptx; .pdf</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>16s</t>
         </is>
       </c>
     </row>
@@ -3918,17 +3934,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3938,7 +3954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3958,18 +3974,18 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Incompleto</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>DOCX, PPT, PDF</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr"/>
+          <t>Aguardando AJ1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>U01A02_Fisioterapia na Saúde do Idoso_Rev1.docx; U01A02_Fisioterapia na Saúde do Idoso_Rev1.pptx; U01A02_FUNDAMENTOS DO ENVELHECIMENTO E ATENÇÃO À SAÚDE DA PESSOA IDOSA__Template_ENTREGA.pptx; U01A02_FUNDAMENTOSDOENVELHECIMENTOEATENÇÃOÀSAÚDEDAPESSOAIDOSA_ENTREGA.docx; U01A02_FUNDAMENTOSDOENVELHECIMENTOEATENCAOASAUDEDAPESSOAIDOSA_ENTREGA-report.pdf; .docx; .pptx; .pdf</t>
+        </is>
+      </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>11s</t>
+          <t>16s</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4083,7 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
-          <t>11s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4181,7 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
-          <t>11s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4279,7 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
-          <t>11s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4381,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>17s</t>
+          <t>14s</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4479,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>16s</t>
+          <t>14s</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4577,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>15s</t>
+          <t>14s</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4675,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>18s</t>
+          <t>14s</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4773,7 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>11s</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4840,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4844,13 +4860,13 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Entrega inicial completa</t>
+          <t>Aguardando AJ1</t>
         </is>
       </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>U01A01_FISIOTERAPIAPÉLVICAEDISFUNÇÕESDOASSOALHOPÉLVICO_ENTREGA.docx; U01A01_FISIOTERAPIAPÉLVICAEDISFUNÇÕESDOASSOALHOPÉLVICO_ENTREGA.pptx; U01A01_FISIOTERAPIAPELVICAEDISFUNCOESDOASSOALHOPELVICO_ENTREGA-report.pdf; .docx; .pptx; .pdf</t>
+          <t>U01A01_Fisioterapia na Saúde da Mulher_Rev1.docx; U01A01_Fisioterapia na Saúde da Mulher_Rev1.pptx; U01A01_FISIOTERAPIAPÉLVICAEDISFUNÇÕESDOASSOALHOPÉLVICO_ENTREGA.docx; U01A01_FISIOTERAPIAPÉLVICAEDISFUNÇÕESDOASSOALHOPÉLVICO_ENTREGA.pptx; U01A01_FISIOTERAPIAPELVICAEDISFUNCOESDOASSOALHOPELVICO_ENTREGA-report.pdf; .docx; .pptx; .pdf</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -4953,7 +4969,7 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
         <is>
-          <t>12s</t>
+          <t>11s</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5067,7 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
         <is>
-          <t>14s</t>
+          <t>11s</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5263,7 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>11s</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5361,7 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5459,7 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>11s</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5557,7 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>11s</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5655,7 @@
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>14s</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5753,7 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
-          <t>14s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -5830,12 +5846,12 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>AULA_U1A01_Atividades Físicas em Academia _ Aprovado.docx; AULA_U1A01_Atividades Físicas em Academia.docx; AULA_U1A01_Atividades_Fisicas_em_Academia_Relatorio.pdf; BQ_U1A01_Atividades Físicas em Academia _ Aprovado.docx; BQ_U1A01_Atividades Físicas em Academia.docx; SL_U1A01_Atividades Físicas em Academia.pptx; SL_U1A01_Atividades Físicas em Academia_ REV01.pptx; SL_U1A01_Atividades Físicas em Academia_AJ01.pptx; .docx; .pdf; .pptx</t>
+          <t>AULA_U1A01_Atividades Físicas em Academia _ Aprovado.docx; AULA_U1A01_Atividades Físicas em Academia.docx; AULA_U1A01_Atividades_Fisicas_em_Academia_Relatorio.pdf; BQ_U1A01_Atividades Físicas em Academia _ Aprovado.docx; BQ_U1A01_Atividades Físicas em Academia.docx; SL_U1A01_Atividades Físicas em Academia.pptx; SL_U1A01_Atividades Físicas em Academia_ Aprovado.pptx; SL_U1A01_Atividades Físicas em Academia_AJ01.pptx; .docx; .pdf; .pptx</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>23s</t>
+          <t>18s</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5928,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5922,13 +5938,13 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Entrega inicial completa</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>AULA_U1A02_Atividades Físicas em Academia.docx; AULA_U1A02_Atividades_Fisicas_em_Academia_Relatorio.pdf; BQ_U1A02_Atividades Físicas em Academia.docx; SL_U1A02_Atividades Físicas em Academia.pptx; .docx; .pdf; .pptx</t>
+          <t>AULA_U1A02_Atividades Físicas em Academia.docx; AULA_U1A02_Atividades Físicas em Academia_Aprovado.docx; AULA_U1A02_Atividades_Fisicas_em_Academia_Relatorio.pdf; BQ_U1A02_Atividades Físicas em Academia _Aprovado.docx; BQ_U1A02_Atividades Físicas em Academia.docx; SL_U1A02_Atividades Físicas em Academia _ Aprovado.pptx; SL_U1A02_Atividades Físicas em Academia.pptx; .docx; .pdf; .pptx</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -5980,17 +5996,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>FALTANDO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6020,18 +6036,18 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Incompleto</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>DOCX, PPT, PDF</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr"/>
+          <t>Entrega inicial completa</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>AULA_U1A03_Atividades Físicas em Academia.docx; AULA_U1A03_Atividades_Fisicas_em_Academia_Relatorio.pdf; BQ_U1A03_Atividades Físicas em Academia.docx; SL_U1A03_Atividades Físicas em Academia.pptx; .docx; .pdf; .pptx</t>
+        </is>
+      </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>18s</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6145,7 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
-          <t>18s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6243,7 @@
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>11s</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6341,7 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
-          <t>13s</t>
+          <t>12s</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7027,7 @@
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr">
         <is>
-          <t>12s</t>
+          <t>11s</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7223,7 @@
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr">
         <is>
-          <t>12s</t>
+          <t>11s</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7260,11 +7276,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Incompleto</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -7280,11 +7296,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Incompleto</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -7440,7 +7456,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Entrega inicial completa</t>
+          <t>Aguardando AJ1</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -7464,7 +7480,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -7480,11 +7496,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Entrega inicial completa</t>
+          <t>Aguardando AJ1</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -7504,7 +7520,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -7530,7 +7546,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FISIOTERAPIA NEUROFUNCIONAL</t>
+          <t>FISIOTERAPIA NA SAUDE DO TRABALHADOR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7540,17 +7556,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Incompleto</t>
+          <t>Entrega inicial completa</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GOVERNANCA E QUALIDADE DE DADOS</t>
+          <t>FISIOTERAPIA NEUROFUNCIONAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7564,23 +7580,23 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LAVRA DE MINAS</t>
+          <t>FISIOTERAPIA NEUROFUNCIONAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Incompleto</t>
+          <t>Entrega inicial completa</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -7590,7 +7606,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OLERICULTURA</t>
+          <t>GOVERNANCA E QUALIDADE DE DADOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7610,7 +7626,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PERFURAÇÃO E DESMONTE DE ROCHAS</t>
+          <t>LAVRA DE MINAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7630,7 +7646,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PRESCRICAO DO EXERCICIO PARA GRUPOS ESPECIAIS</t>
+          <t>OLERICULTURA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7644,27 +7660,27 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PRESCRICAO DO EXERCICIO PARA GRUPOS ESPECIAIS</t>
+          <t>PERFURAÇÃO E DESMONTE DE ROCHAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Incompleto</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -7680,30 +7696,70 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Entrega inicial completa</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>PRESCRICAO DO EXERCICIO PARA GRUPOS ESPECIAIS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Incompleto</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PRESCRICAO DO EXERCICIO PARA GRUPOS ESPECIAIS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Entrega inicial completa</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>PROJETO DE FABRICA E INSTALACOES INDUSTRIAIS</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Incompleto</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D26" t="n">
         <v>5</v>
       </c>
     </row>
